--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0017.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0017.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tôi vẫn thường hái quả Mận Pavo quanh khu vực này. Nhưng theo &lt;i&gt;Hồng Trấn Ký Lục&lt;/i&gt;, chỉ những quả "mọc gần suối nước nóng và có thể hơi ấm lên một chút" mới có tác dụng chữa bệnh.</t>
+          <t>Tôi vẫn thường hái quả Mận Pavo quanh khu vực này. Nhưng theo &lt;i&gt;Hongzhen Ký Lục&lt;/i&gt;, chỉ những quả "mọc gần suối nước nóng và có thể hơi ấm lên một chút" mới có tác dụng chữa bệnh.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Thứ gì cũng được, tốt nhất là dài và phức tạp. Ta muốn thử xem nó có thật sự giúp cải thiện trí nhớ không.</t>
+          <t>Thứ gì cũng được, tốt nhất là dài và phức tạp. Tao muốn thử xem nó có thật sự giúp cải thiện trí nhớ không.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Nóng quá đi! Ta đã nếm vô số loại thảo dược, nhưng chưa bao giờ thấy cay đến thế này!</t>
+          <t>Nóng quá đi! Tao đã nếm vô số loại thảo dược, nhưng chưa bao giờ thấy cay đến thế này!</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Ừm... Chính là anh/cậu đấy, {PlayerName}.</t>
+          <t>Ừm... Chính là bạn đấy, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Ta lỡ trượt chân ngã xuống đồi. May mà chỉ bị sưng chân thôi.</t>
+          <t>Tao lỡ trượt chân ngã xuống đồi. May mà chỉ bị sưng chân thôi.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cứ giao cho ta!</t>
+          <t>Cứ giao cho tao!</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Gần đây ta đã đạt được nhiều tiến bộ và đã hoàn thành việc chỉnh sửa dược điển ở Hồng Trấn.</t>
+          <t>Gần đây ta đã đạt được nhiều tiến bộ và đã hoàn thành việc chỉnh sửa dược điển ở Hongzhen.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Lệnh thuyên chuyển của ta chắc cũng sắp về rồi. Sau đó ta sẽ phải quay về Jinzhou mà giải thích với sếp về mớ hỗn độn này.</t>
+          <t>Lệnh thuyên chuyển của tao chắc cũng sắp về rồi. Sau đó tao sẽ phải quay về Jinzhou mà giải thích với sếp về mớ hỗn độn này.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ban đầu hắn không hề có ý định mua hàng của chúng ta, nhưng lại tình cờ gặp nhà nghiên cứu đó ở Hồng Trấn trong một chuyến công tác.</t>
+          <t>Ban đầu hắn không hề có ý định mua hàng của chúng ta, nhưng lại tình cờ gặp nhà nghiên cứu đó ở Hongzhen trong một chuyến công tác.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Thở dài. Ta cũng biết mà... Thật sự không hiểu ông sếp nghĩ gì nữa...</t>
+          <t>Thở dài. Tao cũng biết mà... Thật sự không hiểu ông sếp nghĩ gì nữa...</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nhiều lắm. Trước khi làm sales, ta từng làm dịch vụ khách hàng.</t>
+          <t>Nhiều lắm. Trước khi làm sales, tao từng làm dịch vụ khách hàng.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Ừ! Đây là lần đầu quý khách đến Hồng Trấn và muốn mua gì à? Vậy thì quý khách đến đúng chỗ rồi!</t>
+          <t>Ừ! Đây là lần đầu bạn đến Hongzhen và muốn mua gì à? Vậy thì bạn đến đúng chỗ rồi!</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Không phải đâu. Tớ mang nó từ Kim Châu về cơ!</t>
+          <t>Không phải đâu. Tớ mang nó từ Jinzhou về cơ!</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Nghe có vẻ khả nghi đấy. Nếu đá không vấn đề gì, sao cậu lại căng thẳng thế?</t>
+          <t>Nghe có vẻ khả nghi đấy. Nếu đá không vấn đề gì, sao mày lại căng thẳng thế?</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Thôi nào, ta đâu có đùa với ngươi. Không tin à? Nhìn cái đấy đi!</t>
+          <t>Thôi nào, tao đâu có đùa với mày. Không tin à? Nhìn cái đấy đi!</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Suối nước nóng của quý khách trông thật quyến rũ.</t>
+          <t>Suối nước nóng của bạn trông thật quyến rũ, thưa quý khách.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>À, sếp mình chẳng bao giờ lạc quan về Hồng Trấn đâu, nếu không thì đã chẳng cử một kẻ dưới đáy như mình đến đây.</t>
+          <t>À, sếp mình chẳng bao giờ lạc quan về Hongzhen đâu, nếu không thì đã chẳng cử một kẻ dưới đáy như mình đến đây.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Ha.. haha... Ồ, vậy à? À phải... hình như ta có nhắc đến chuyện đó thật.</t>
+          <t>Ha.. haha... Ồ, vậy à? À phải... hình như tao có nhắc đến chuyện đó thật.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Nhưng giá này tôi đưa ra đã rất thấp rồi... Chúng ta còn phải vận chuyển đá từ tận Kim Châu về, chưa kể có thể gặp phải Tổ Tacet trên đường nữa...</t>
+          <t>Nhưng giá này tôi đưa ra đã rất thấp rồi... Chúng ta còn phải vận chuyển đá từ tận Jinzhou về, chưa kể có thể gặp phải Tổ Tacet trên đường nữa...</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Sao, ta...?</t>
+          <t>Sao, tao...?</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Để ta kể cho cậu nghe về truyền thuyết khác của Núi Vòm Trời, vì sâu trong những đỉnh núi linh thiêng ấy ẩn chứa một bí mật quyền năng... "Bí Mật Bất Tử"!</t>
+          <t>Để ta kể cho cậu nghe về truyền thuyết khác của Mt. Firmament, vì sâu trong những đỉnh núi linh thiêng ấy ẩn chứa một bí mật quyền năng... "Bí Mật Bất Tử"!</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hừm... "Ngắm nhìn toàn cảnh Hồng Trấn bên vành đai và mái hiên rủ bóng. Khi tuyết vĩnh cửu tan thành dòng suối, ta sẽ hội ngộ."</t>
+          <t>Hừm... "Ngắm nhìn toàn cảnh Hongzhen bên vành đai và mái hiên rủ bóng. Khi tuyết vĩnh cửu tan thành dòng suối, ta sẽ hội ngộ."</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Ta có kinh nghiệm rồi. Mấy câu đố của Jinhsi ta đã gặp rồi.</t>
+          <t>Tao có kinh nghiệm rồi. Mấy câu đố của Jinhsi tao đã gặp rồi.</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Nhưng các tòa nhà ở Hồng Trấn nhìn chẳng khác gì nhau cả. Rốt cuộc cô ấy nói về tòa nào nhỉ?</t>
+          <t>Nhưng các tòa nhà ở Hongzhen nhìn chẳng khác gì nhau cả. Rốt cuộc cô ấy nói về tòa nào nhỉ?</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Ta có thể hỏi xung quanh để tìm hiểu. Ta từng làm việc này rồi.</t>
+          <t>Ta có thể hỏi xung quanh để tìm hiểu. Tao từng làm việc này rồi.</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tôi... tôi không sao. Khoan, cậu... Cậu chính là Rover...?</t>
+          <t>Tôi... tôi không sao. Khoan, cậu... Cậu chính là Vận Mệnh Giả...?</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ta không thể chết ở đây. Không phải khi vẫn còn người đang đợi ta...</t>
+          <t>Tao không thể chết ở đây. Không phải khi vẫn còn người đang đợi tao...</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Hắn cần được đưa về Hồng Trấn để điều trị đúng cách... Thời gian không còn nhiều nữa.</t>
+          <t>Hắn cần được đưa về Hongzhen để điều trị đúng cách... Thời gian không còn nhiều nữa.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đúng đấy, Rover. Quay lại thôi.</t>
+          <t>Đúng đấy, Vận Mệnh Giả. Quay lại thôi.</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Chắc hẳn hắn là fan của ông kể chuyện ở Kim Châu rồi.</t>
+          <t>Chắc hẳn hắn là fan của ông kể chuyện ở Jinzhou rồi.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đúng rồi, Fuling, bạn gái của cậu ấy. Tớ nghĩ hai người đang đi thăm Hồng Trấn cùng nhau. Họ đang ở quán trọ đằng kia.</t>
+          <t>Đúng rồi, Fuling, bạn gái của cậu ấy. Tớ nghĩ hai người đang đi thăm Hongzhen cùng nhau. Họ đang ở quán trọ đằng kia.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>W-Wuli! Ta... *ho*...</t>
+          <t>W-Wuli! Tao... *ho*...</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Dù đã cố gắng hết sức, chúng tôi vẫn không tìm ra cách chữa trị... Cho đến hai tuần trước, khi ông đưa ta đến Hongzhen. Ông bảo có điều bất ngờ dành cho ta.</t>
+          <t>Dù đã cố gắng hết sức, chúng tôi vẫn không tìm ra cách chữa trị... Cho đến hai tuần trước, khi ông đưa tao đến Hongzhen. Ông bảo có điều bất ngờ dành cho tao.</t>
         </is>
       </c>
     </row>
